--- a/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_r2/staggered_7d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_r2/staggered_7d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -468,7 +468,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -477,7 +477,7 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.07932647690083661</v>
+        <v>0.1102016108966168</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.1033355855258853</v>
+        <v>0.1348975223211684</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.3234158994806718</v>
+        <v>0.2620274364057891</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2690410206773099</v>
+        <v>0.1942488708478035</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.3817857897128002</v>
+        <v>0.5246716172108395</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.5505806273793823</v>
+        <v>0.7544522053280546</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.5467107031625715</v>
+        <v>0.8292988737320193</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.2314950792797315</v>
+        <v>0.2017283653456454</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.173306274657461</v>
+        <v>0.1226330784089791</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.3891857803903652</v>
+        <v>0.6216179687477351</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>23.10033325040832</v>
+        <v>26.23662502275658</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1590550288239375</v>
+        <v>-0.1736926964930503</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.08589935870139564</v>
+        <v>0.06699796267717706</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2824767201434192</v>
+        <v>0.2513946954149336</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1937576405027788</v>
+        <v>0.1559666887026701</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.5502742923711794</v>
+        <v>-0.723609095250886</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.7546284694809734</v>
+        <v>-0.9664065742004543</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.5358966120406485</v>
+        <v>0.4960177902993731</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2429259259835121</v>
+        <v>0.2272717575644064</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1308491888108863</v>
+        <v>0.1090028899523029</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.6794384255303686</v>
+        <v>-0.7928021833736425</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>22.61240850060276</v>
+        <v>24.67966032151914</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.2148056761772021</v>
+        <v>-0.1647340720573044</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.1136061678810681</v>
+        <v>-0.05708110178011228</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2576356381214674</v>
+        <v>0.2151822443587289</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1979427674530436</v>
+        <v>0.145155860234264</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.9065431726365448</v>
+        <v>-0.8328499023355646</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-1.274615208347956</v>
+        <v>-1.159667084120914</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.5131756959594924</v>
+        <v>-0.3254164165557589</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.3160218851350243</v>
+        <v>0.2889224866378506</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1911899579096898</v>
+        <v>0.1390851310452786</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.7044222203241204</v>
+        <v>-0.591590926447554</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>27.20186486387604</v>
+        <v>26.91966962634606</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.06313296034091354</v>
+        <v>-0.03425655293182406</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.1707726078968337</v>
+        <v>-0.1452139031975408</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.3098373140320044</v>
+        <v>0.2658612950870361</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1722166201247757</v>
+        <v>0.1282027721889095</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.115271869258417</v>
+        <v>-0.06199377018799589</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1873375929625039</v>
+        <v>-0.1004245119429321</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.007861037493821</v>
+        <v>-1.203847908064342</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2706409001916605</v>
+        <v>0.2771384617454239</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1953086962046565</v>
+        <v>0.2143988636673476</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.2425879500599375</v>
+        <v>-0.1286237341966174</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>26.46055623493105</v>
+        <v>27.96785467322866</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3442861680925682</v>
+        <v>0.2964859962227742</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.09798567253686841</v>
+        <v>0.05894346180557219</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.3094275740027942</v>
+        <v>0.2466404973207779</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1927082885332673</v>
+        <v>0.1269273174673376</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.098911840935801</v>
+        <v>1.15545709642199</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.589806987374913</v>
+        <v>1.655943678884345</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.6793340719106163</v>
+        <v>0.5976821677523003</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.2011995599341581</v>
+        <v>0.1791911203659523</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.168414975579672</v>
+        <v>0.1386017047902406</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.784783809845083</v>
+        <v>1.724496037507248</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>26.19739071511446</v>
+        <v>28.33128001751986</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.2026337199136623</v>
+        <v>0.2480486190260334</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.220999300944003</v>
+        <v>0.267107737079181</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.3756044216719406</v>
+        <v>0.3024032285029721</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2474697819650279</v>
+        <v>0.1830159220524692</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.045544900710486</v>
+        <v>1.440292818005964</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.480081725205207</v>
+        <v>2.085958610597975</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.652868690363779</v>
+        <v>2.469036353475497</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1421767605015072</v>
+        <v>0.1178664400702621</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.09113958690607804</v>
+        <v>0.07509851081363872</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.81799123200204</v>
+        <v>4.231422843293877</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>23.90710933030052</v>
+        <v>27.6783653093619</v>
       </c>
     </row>
   </sheetData>
